--- a/files/九龙-西南九龙-维港汇 III.xlsx
+++ b/files/九龙-西南九龙-维港汇 III.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>1408</v>
+        <v>1394</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         <v>66330000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>47109</v>
+        <v>47582</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>66330000</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>47109</v>
+        <v>47582</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
@@ -24918,9 +24918,9 @@
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>B | 1408呎 (4+房)
+          <t>B | 1394呎 (4+房)
 $6633万
-$47,109/呎
+$47,582/呎
 (21年-04月-30日)</t>
         </is>
       </c>

--- a/files/九龙-西南九龙-维港汇 III.xlsx
+++ b/files/九龙-西南九龙-维港汇 III.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>1394</v>
+        <v>1408</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         <v>66330000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>47582</v>
+        <v>47109</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>66330000</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>47582</v>
+        <v>47109</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>30980000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>33348</v>
+        <v>30949</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>30980000</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>33348</v>
+        <v>30949</v>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>920</v>
+        <v>977</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>30880000</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>33565</v>
+        <v>31607</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>30880000</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>33565</v>
+        <v>31607</v>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>30780000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>33132</v>
+        <v>30749</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>30780000</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>33132</v>
+        <v>30749</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>920</v>
+        <v>977</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>30800000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>33478</v>
+        <v>31525</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>30800000</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>33478</v>
+        <v>31525</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>30380000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>32702</v>
+        <v>30350</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>30380000</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>32702</v>
+        <v>30350</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>920</v>
+        <v>977</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>31500000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>34239</v>
+        <v>32242</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>31500000</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>34239</v>
+        <v>32242</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>30800000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>33154</v>
+        <v>30769</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>30800000</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>33154</v>
+        <v>30769</v>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>920</v>
+        <v>977</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>30280000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>32913</v>
+        <v>30993</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>30280000</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>32913</v>
+        <v>30993</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>30720000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>33068</v>
+        <v>30689</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>30720000</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>33068</v>
+        <v>30689</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>920</v>
+        <v>977</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>32000000</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>34783</v>
+        <v>32753</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>32000000</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>34783</v>
+        <v>32753</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>30180000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>32487</v>
+        <v>30150</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>30180000</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>32487</v>
+        <v>30150</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>920</v>
+        <v>977</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>29880000</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>32478</v>
+        <v>30583</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>29880000</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>32478</v>
+        <v>30583</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>29980000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>32271</v>
+        <v>29950</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>29980000</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>32271</v>
+        <v>29950</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>920</v>
+        <v>977</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>29830000</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>32424</v>
+        <v>30532</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>29830000</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>32424</v>
+        <v>30532</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>29880000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>32164</v>
+        <v>29850</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>29880000</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>32164</v>
+        <v>29850</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>30080000</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>32379</v>
+        <v>30050</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>30080000</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>32379</v>
+        <v>30050</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>920</v>
+        <v>977</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>29730000</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>32315</v>
+        <v>30430</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>29730000</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>32315</v>
+        <v>30430</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>29190000</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>31421</v>
+        <v>29161</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>29190000</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>31421</v>
+        <v>29161</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>920</v>
+        <v>977</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>29680000</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>32261</v>
+        <v>30379</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>29680000</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>32261</v>
+        <v>30379</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>30000000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>32293</v>
+        <v>29970</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>30000000</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>32293</v>
+        <v>29970</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>920</v>
+        <v>977</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>29580000</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>32152</v>
+        <v>30276</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>29580000</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>32152</v>
+        <v>30276</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>28800000</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>31001</v>
+        <v>28771</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>28800000</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>31001</v>
+        <v>28771</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>920</v>
+        <v>977</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>30000000</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>32609</v>
+        <v>30706</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>30000000</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>32609</v>
+        <v>30706</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>29380000</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>31625</v>
+        <v>29351</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>29380000</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>31625</v>
+        <v>29351</v>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>28600000</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>30786</v>
+        <v>28571</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>28600000</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>30786</v>
+        <v>28571</v>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>29380000</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>31625</v>
+        <v>29351</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>29380000</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>31625</v>
+        <v>29351</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>28280000</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>30441</v>
+        <v>28252</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>28280000</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>30441</v>
+        <v>28252</v>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>920</v>
+        <v>977</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>28500000</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>30978</v>
+        <v>29171</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>28500000</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>30978</v>
+        <v>29171</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>28000000</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>30140</v>
+        <v>27972</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>28000000</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>30140</v>
+        <v>27972</v>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>27880000</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>30011</v>
+        <v>27852</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>27880000</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>30011</v>
+        <v>27852</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>27880000</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>30011</v>
+        <v>27852</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>27880000</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>30011</v>
+        <v>27852</v>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>920</v>
+        <v>977</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>28480000</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>30957</v>
+        <v>29150</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>28480000</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>30957</v>
+        <v>29150</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>27700000</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>29817</v>
+        <v>27672</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>27700000</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>29817</v>
+        <v>27672</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>27600000</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>29709</v>
+        <v>27572</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>27600000</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>29709</v>
+        <v>27572</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>920</v>
+        <v>977</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>27220000</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>29587</v>
+        <v>27861</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>27220000</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>29587</v>
+        <v>27861</v>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>27500000</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>29602</v>
+        <v>27473</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>27500000</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>29602</v>
+        <v>27473</v>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>920</v>
+        <v>977</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>27000000</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>29348</v>
+        <v>27636</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>27000000</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>29348</v>
+        <v>27636</v>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>27380000</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>29473</v>
+        <v>27353</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>27380000</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>29473</v>
+        <v>27353</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>920</v>
+        <v>977</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>26650000</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>28967</v>
+        <v>27277</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>26650000</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>28967</v>
+        <v>27277</v>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>27020000</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>29085</v>
+        <v>26993</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>27020000</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>29085</v>
+        <v>26993</v>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>920</v>
+        <v>977</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>26330000</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>28620</v>
+        <v>26950</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>26330000</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>28620</v>
+        <v>26950</v>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>26520000</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>28547</v>
+        <v>26494</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>26520000</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>28547</v>
+        <v>26494</v>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>920</v>
+        <v>977</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>26430000</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>28728</v>
+        <v>27052</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>26430000</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>28728</v>
+        <v>27052</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>893</v>
+        <v>964</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>29453000</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>32982</v>
+        <v>30553</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>29453000</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>32982</v>
+        <v>30553</v>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>869</v>
+        <v>925</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>27000000</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>31070</v>
+        <v>29189</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>27000000</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>31070</v>
+        <v>29189</v>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>7457700</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>25195</v>
+        <v>26730</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>7457700</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>25195</v>
+        <v>26730</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>7723300</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>27782</v>
+        <v>27882</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>7723300</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>27782</v>
+        <v>27882</v>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>8663900</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>26254</v>
+        <v>26175</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>8663900</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>26254</v>
+        <v>26175</v>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>8652800</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>27210</v>
+        <v>27296</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>8652800</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>27210</v>
+        <v>27296</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>6866400</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>24699</v>
+        <v>24611</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>6866400</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>24699</v>
+        <v>24611</v>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>8493700</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>25738</v>
+        <v>25661</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>8493700</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>25738</v>
+        <v>25661</v>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>8482600</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>26675</v>
+        <v>26759</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>8482600</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>26675</v>
+        <v>26759</v>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>8544000</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>25891</v>
+        <v>25813</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>8544000</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>25891</v>
+        <v>25813</v>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>7497300</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>26969</v>
+        <v>27066</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>7497300</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>26969</v>
+        <v>27066</v>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>8409300</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>25483</v>
+        <v>25406</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>8409300</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>25483</v>
+        <v>25406</v>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>9589900</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>30157</v>
+        <v>30252</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>9589900</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>30157</v>
+        <v>30252</v>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>8501800</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>25763</v>
+        <v>25685</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>8501800</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>25763</v>
+        <v>25685</v>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>7782400</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>27994</v>
+        <v>28095</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>7782400</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>27994</v>
+        <v>28095</v>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>8367900</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>25357</v>
+        <v>25281</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>8367900</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>25357</v>
+        <v>25281</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>9147300</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>28765</v>
+        <v>28856</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>9147300</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>28765</v>
+        <v>28856</v>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>8460400</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>25638</v>
+        <v>25560</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>8460400</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>25638</v>
+        <v>25560</v>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>8367900</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>25357</v>
+        <v>25281</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>8367900</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>25357</v>
+        <v>25281</v>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>9101100</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>28620</v>
+        <v>28710</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>9101100</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>28620</v>
+        <v>28710</v>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>8417500</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>25508</v>
+        <v>25431</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>8417500</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>25508</v>
+        <v>25431</v>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>8284300</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>25104</v>
+        <v>25028</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>8284300</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>25104</v>
+        <v>25028</v>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>9447100</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>29708</v>
+        <v>29802</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>9447100</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>29708</v>
+        <v>29802</v>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>8376000</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>25382</v>
+        <v>25305</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>8376000</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>25382</v>
+        <v>25305</v>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>8243600</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>24981</v>
+        <v>24905</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>8243600</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>24981</v>
+        <v>24905</v>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         </is>
       </c>
       <c r="E104" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>8334600</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>25256</v>
+        <v>25180</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>8334600</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>25256</v>
+        <v>25180</v>
       </c>
       <c r="M104" s="3" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         </is>
       </c>
       <c r="E106" s="4" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>7628600</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>27441</v>
+        <v>27540</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>7628600</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>27441</v>
+        <v>27540</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         </is>
       </c>
       <c r="E107" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>8202100</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>24855</v>
+        <v>24780</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>8202100</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>24855</v>
+        <v>24780</v>
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         </is>
       </c>
       <c r="E108" s="4" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>9354100</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>29415</v>
+        <v>29508</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>9354100</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>29415</v>
+        <v>29508</v>
       </c>
       <c r="M108" s="3" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>8292400</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>25128</v>
+        <v>25053</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>8292400</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>25128</v>
+        <v>25053</v>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>8161400</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>24732</v>
+        <v>24657</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>8161400</v>
       </c>
       <c r="L114" s="5" t="n">
-        <v>24732</v>
+        <v>24657</v>
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>8151100</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>25632</v>
+        <v>25713</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>8151100</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>25632</v>
+        <v>25713</v>
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         </is>
       </c>
       <c r="E118" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>9031500</v>
       </c>
       <c r="I118" s="5" t="n">
-        <v>27368</v>
+        <v>27285</v>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         <v>9031500</v>
       </c>
       <c r="L118" s="5" t="n">
-        <v>27368</v>
+        <v>27285</v>
       </c>
       <c r="M118" s="3" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="E120" s="4" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>7553400</v>
       </c>
       <c r="I120" s="5" t="n">
-        <v>27171</v>
+        <v>27269</v>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>7553400</v>
       </c>
       <c r="L120" s="5" t="n">
-        <v>27171</v>
+        <v>27269</v>
       </c>
       <c r="M120" s="3" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         </is>
       </c>
       <c r="E121" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>8120700</v>
       </c>
       <c r="I121" s="5" t="n">
-        <v>24608</v>
+        <v>24534</v>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>8120700</v>
       </c>
       <c r="L121" s="5" t="n">
-        <v>24608</v>
+        <v>24534</v>
       </c>
       <c r="M121" s="3" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="E122" s="4" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>9261200</v>
       </c>
       <c r="I122" s="5" t="n">
-        <v>29123</v>
+        <v>29215</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>9261200</v>
       </c>
       <c r="L122" s="5" t="n">
-        <v>29123</v>
+        <v>29215</v>
       </c>
       <c r="M122" s="3" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="E127" s="4" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>7515400</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>27034</v>
+        <v>27131</v>
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>7515400</v>
       </c>
       <c r="L127" s="5" t="n">
-        <v>27034</v>
+        <v>27131</v>
       </c>
       <c r="M127" s="3" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         </is>
       </c>
       <c r="E128" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>8845200</v>
       </c>
       <c r="I128" s="5" t="n">
-        <v>26804</v>
+        <v>26723</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>8845200</v>
       </c>
       <c r="L128" s="5" t="n">
-        <v>26804</v>
+        <v>26723</v>
       </c>
       <c r="M128" s="3" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="E129" s="4" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>8833000</v>
       </c>
       <c r="I129" s="5" t="n">
-        <v>27777</v>
+        <v>27864</v>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>8833000</v>
       </c>
       <c r="L129" s="5" t="n">
-        <v>27777</v>
+        <v>27864</v>
       </c>
       <c r="M129" s="3" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         </is>
       </c>
       <c r="E132" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>8169600</v>
       </c>
       <c r="I132" s="5" t="n">
-        <v>24756</v>
+        <v>24682</v>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>8169600</v>
       </c>
       <c r="L132" s="5" t="n">
-        <v>24756</v>
+        <v>24682</v>
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         </is>
       </c>
       <c r="E134" s="4" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>7168500</v>
       </c>
       <c r="I134" s="5" t="n">
-        <v>25786</v>
+        <v>25879</v>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>7168500</v>
       </c>
       <c r="L134" s="5" t="n">
-        <v>25786</v>
+        <v>25879</v>
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="E135" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         <v>8040100</v>
       </c>
       <c r="I135" s="5" t="n">
-        <v>24364</v>
+        <v>24290</v>
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>8040100</v>
       </c>
       <c r="L135" s="5" t="n">
-        <v>24364</v>
+        <v>24290</v>
       </c>
       <c r="M135" s="3" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="E136" s="4" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>8029700</v>
       </c>
       <c r="I136" s="5" t="n">
-        <v>25251</v>
+        <v>25330</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>8029700</v>
       </c>
       <c r="L136" s="5" t="n">
-        <v>25251</v>
+        <v>25330</v>
       </c>
       <c r="M136" s="3" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         </is>
       </c>
       <c r="E139" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>8897800</v>
       </c>
       <c r="I139" s="5" t="n">
-        <v>26963</v>
+        <v>26882</v>
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>8897800</v>
       </c>
       <c r="L139" s="5" t="n">
-        <v>26963</v>
+        <v>26882</v>
       </c>
       <c r="M139" s="3" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         </is>
       </c>
       <c r="E146" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>8128900</v>
       </c>
       <c r="I146" s="5" t="n">
-        <v>24633</v>
+        <v>24559</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>8128900</v>
       </c>
       <c r="L146" s="5" t="n">
-        <v>24633</v>
+        <v>24559</v>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="E148" s="4" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>7132800</v>
       </c>
       <c r="I148" s="5" t="n">
-        <v>25658</v>
+        <v>25750</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>7132800</v>
       </c>
       <c r="L148" s="5" t="n">
-        <v>25658</v>
+        <v>25750</v>
       </c>
       <c r="M148" s="3" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         </is>
       </c>
       <c r="E149" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         <v>8756900</v>
       </c>
       <c r="I149" s="5" t="n">
-        <v>26536</v>
+        <v>26456</v>
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>8756900</v>
       </c>
       <c r="L149" s="5" t="n">
-        <v>26536</v>
+        <v>26456</v>
       </c>
       <c r="M149" s="3" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         </is>
       </c>
       <c r="E155" s="4" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>7367500</v>
       </c>
       <c r="I155" s="5" t="n">
-        <v>26502</v>
+        <v>26597</v>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>7367500</v>
       </c>
       <c r="L155" s="5" t="n">
-        <v>26502</v>
+        <v>26597</v>
       </c>
       <c r="M155" s="3" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         </is>
       </c>
       <c r="E157" s="4" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>8658900</v>
       </c>
       <c r="I157" s="5" t="n">
-        <v>27229</v>
+        <v>27315</v>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>8658900</v>
       </c>
       <c r="L157" s="5" t="n">
-        <v>27229</v>
+        <v>27315</v>
       </c>
       <c r="M157" s="3" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         </is>
       </c>
       <c r="E160" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>8766600</v>
       </c>
       <c r="I160" s="5" t="n">
-        <v>26565</v>
+        <v>26485</v>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>8766600</v>
       </c>
       <c r="L160" s="5" t="n">
-        <v>26565</v>
+        <v>26485</v>
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         </is>
       </c>
       <c r="E163" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>9000000</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>27273</v>
+        <v>27190</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>9000000</v>
       </c>
       <c r="L163" s="5" t="n">
-        <v>27273</v>
+        <v>27190</v>
       </c>
       <c r="M163" s="3" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         </is>
       </c>
       <c r="E164" s="4" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>8510400</v>
       </c>
       <c r="I164" s="5" t="n">
-        <v>26762</v>
+        <v>26847</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>8510400</v>
       </c>
       <c r="L164" s="5" t="n">
-        <v>26762</v>
+        <v>26847</v>
       </c>
       <c r="M164" s="3" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         </is>
       </c>
       <c r="E170" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>8955300</v>
       </c>
       <c r="I170" s="5" t="n">
-        <v>27137</v>
+        <v>27055</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>8955300</v>
       </c>
       <c r="L170" s="5" t="n">
-        <v>27137</v>
+        <v>27055</v>
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="E181" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>7889100</v>
       </c>
       <c r="I181" s="5" t="n">
-        <v>23906</v>
+        <v>23834</v>
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>7889100</v>
       </c>
       <c r="L181" s="5" t="n">
-        <v>23906</v>
+        <v>23834</v>
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         </is>
       </c>
       <c r="E188" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
@@ -12243,7 +12243,7 @@
         <v>8593200</v>
       </c>
       <c r="I188" s="5" t="n">
-        <v>26040</v>
+        <v>25961</v>
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>8593200</v>
       </c>
       <c r="L188" s="5" t="n">
-        <v>26040</v>
+        <v>25961</v>
       </c>
       <c r="M188" s="3" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         </is>
       </c>
       <c r="E190" s="4" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>6888200</v>
       </c>
       <c r="I190" s="5" t="n">
-        <v>24778</v>
+        <v>24867</v>
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>6888200</v>
       </c>
       <c r="L190" s="5" t="n">
-        <v>24778</v>
+        <v>24867</v>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="E191" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>8457200</v>
       </c>
       <c r="I191" s="5" t="n">
-        <v>25628</v>
+        <v>25550</v>
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>8457200</v>
       </c>
       <c r="L191" s="5" t="n">
-        <v>25628</v>
+        <v>25550</v>
       </c>
       <c r="M191" s="3" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         </is>
       </c>
       <c r="E195" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>8964600</v>
       </c>
       <c r="I195" s="5" t="n">
-        <v>27165</v>
+        <v>27083</v>
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>8964600</v>
       </c>
       <c r="L195" s="5" t="n">
-        <v>27165</v>
+        <v>27083</v>
       </c>
       <c r="M195" s="3" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         </is>
       </c>
       <c r="E197" s="4" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>6853400</v>
       </c>
       <c r="I197" s="5" t="n">
-        <v>24653</v>
+        <v>24742</v>
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>6853400</v>
       </c>
       <c r="L197" s="5" t="n">
-        <v>24653</v>
+        <v>24742</v>
       </c>
       <c r="M197" s="3" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         </is>
       </c>
       <c r="E198" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>7687800</v>
       </c>
       <c r="I198" s="5" t="n">
-        <v>23296</v>
+        <v>23226</v>
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>7687800</v>
       </c>
       <c r="L198" s="5" t="n">
-        <v>23296</v>
+        <v>23226</v>
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         </is>
       </c>
       <c r="E199" s="4" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         <v>8663100</v>
       </c>
       <c r="I199" s="5" t="n">
-        <v>27242</v>
+        <v>27328</v>
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>8663100</v>
       </c>
       <c r="L199" s="5" t="n">
-        <v>27242</v>
+        <v>27328</v>
       </c>
       <c r="M199" s="3" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         </is>
       </c>
       <c r="E204" s="4" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>7064900</v>
       </c>
       <c r="I204" s="5" t="n">
-        <v>25413</v>
+        <v>25505</v>
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>7064900</v>
       </c>
       <c r="L204" s="5" t="n">
-        <v>25413</v>
+        <v>25505</v>
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         </is>
       </c>
       <c r="E205" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>8415000</v>
       </c>
       <c r="I205" s="5" t="n">
-        <v>25500</v>
+        <v>25423</v>
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>8415000</v>
       </c>
       <c r="L205" s="5" t="n">
-        <v>25500</v>
+        <v>25423</v>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         </is>
       </c>
       <c r="E209" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>8465300</v>
       </c>
       <c r="I209" s="5" t="n">
-        <v>25652</v>
+        <v>25575</v>
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>8465300</v>
       </c>
       <c r="L209" s="5" t="n">
-        <v>25652</v>
+        <v>25575</v>
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         </is>
       </c>
       <c r="E212" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>7611600</v>
       </c>
       <c r="I212" s="5" t="n">
-        <v>23065</v>
+        <v>22996</v>
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
         <v>7611600</v>
       </c>
       <c r="L212" s="5" t="n">
-        <v>23065</v>
+        <v>22996</v>
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         </is>
       </c>
       <c r="E216" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>8787100</v>
       </c>
       <c r="I216" s="5" t="n">
-        <v>26628</v>
+        <v>26547</v>
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>8787100</v>
       </c>
       <c r="L216" s="5" t="n">
-        <v>26628</v>
+        <v>26547</v>
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         </is>
       </c>
       <c r="E220" s="4" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>8534500</v>
       </c>
       <c r="I220" s="5" t="n">
-        <v>26838</v>
+        <v>26923</v>
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>8534500</v>
       </c>
       <c r="L220" s="5" t="n">
-        <v>26838</v>
+        <v>26923</v>
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
@@ -14521,7 +14521,7 @@
         </is>
       </c>
       <c r="E225" s="4" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>7029500</v>
       </c>
       <c r="I225" s="5" t="n">
-        <v>25286</v>
+        <v>25377</v>
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>7029500</v>
       </c>
       <c r="L225" s="5" t="n">
-        <v>25286</v>
+        <v>25377</v>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="E226" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>8630800</v>
       </c>
       <c r="I226" s="5" t="n">
-        <v>26154</v>
+        <v>26075</v>
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>8630800</v>
       </c>
       <c r="L226" s="5" t="n">
-        <v>26154</v>
+        <v>26075</v>
       </c>
       <c r="M226" s="3" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         </is>
       </c>
       <c r="E230" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>8389900</v>
       </c>
       <c r="I230" s="5" t="n">
-        <v>25424</v>
+        <v>25347</v>
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>8389900</v>
       </c>
       <c r="L230" s="5" t="n">
-        <v>25424</v>
+        <v>25347</v>
       </c>
       <c r="M230" s="3" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         </is>
       </c>
       <c r="E234" s="4" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>8602100</v>
       </c>
       <c r="I234" s="5" t="n">
-        <v>27051</v>
+        <v>27136</v>
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>8602100</v>
       </c>
       <c r="L234" s="5" t="n">
-        <v>27051</v>
+        <v>27136</v>
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         </is>
       </c>
       <c r="E237" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         <v>8630500</v>
       </c>
       <c r="I237" s="5" t="n">
-        <v>26153</v>
+        <v>26074</v>
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>8630500</v>
       </c>
       <c r="L237" s="5" t="n">
-        <v>26153</v>
+        <v>26074</v>
       </c>
       <c r="M237" s="3" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         </is>
       </c>
       <c r="E240" s="4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>8495200</v>
       </c>
       <c r="I240" s="5" t="n">
-        <v>25743</v>
+        <v>25665</v>
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>8495200</v>
       </c>
       <c r="L240" s="5" t="n">
-        <v>25743</v>
+        <v>25665</v>
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
@@ -15761,7 +15761,7 @@
         </is>
       </c>
       <c r="E245" s="4" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>6280000</v>
       </c>
       <c r="I245" s="5" t="n">
-        <v>24531</v>
+        <v>24436</v>
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>6280000</v>
       </c>
       <c r="L245" s="5" t="n">
-        <v>24531</v>
+        <v>24436</v>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         </is>
       </c>
       <c r="E249" s="4" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>8100000</v>
       </c>
       <c r="I249" s="5" t="n">
-        <v>27551</v>
+        <v>27645</v>
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
@@ -16036,7 +16036,7 @@
         <v>8100000</v>
       </c>
       <c r="L249" s="5" t="n">
-        <v>27551</v>
+        <v>27645</v>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
         </is>
       </c>
       <c r="E250" s="4" t="n">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>15000000</v>
       </c>
       <c r="I250" s="5" t="n">
-        <v>30801</v>
+        <v>30864</v>
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>15000000</v>
       </c>
       <c r="L250" s="5" t="n">
-        <v>30801</v>
+        <v>30864</v>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         </is>
       </c>
       <c r="E386" s="4" t="n">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F386" s="3" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>14680000</v>
       </c>
       <c r="I386" s="5" t="n">
-        <v>30082</v>
+        <v>30144</v>
       </c>
       <c r="J386" s="3" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>14680000</v>
       </c>
       <c r="L386" s="5" t="n">
-        <v>30082</v>
+        <v>30144</v>
       </c>
       <c r="M386" s="3" t="inlineStr">
         <is>
@@ -24627,7 +24627,7 @@
         </is>
       </c>
       <c r="E388" s="4" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F388" s="3" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>12000000</v>
       </c>
       <c r="I388" s="5" t="n">
-        <v>29197</v>
+        <v>29126</v>
       </c>
       <c r="J388" s="3" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>12000000</v>
       </c>
       <c r="L388" s="5" t="n">
-        <v>29197</v>
+        <v>29126</v>
       </c>
       <c r="M388" s="3" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         </is>
       </c>
       <c r="E389" s="4" t="n">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F389" s="3" t="inlineStr">
         <is>
@@ -24705,7 +24705,7 @@
         <v>8080000</v>
       </c>
       <c r="I389" s="5" t="n">
-        <v>27766</v>
+        <v>27862</v>
       </c>
       <c r="J389" s="3" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>8080000</v>
       </c>
       <c r="L389" s="5" t="n">
-        <v>27766</v>
+        <v>27862</v>
       </c>
       <c r="M389" s="3" t="inlineStr">
         <is>
@@ -24918,9 +24918,9 @@
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>B | 1394呎 (4+房)
+          <t>B | 1408呎 (4+房)
 $6633万
-$47,582/呎
+$47,109/呎
 (21年-04月-30日)</t>
         </is>
       </c>
@@ -24933,17 +24933,17 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 977呎 (3房)
 $3088万
-$33,565/呎
+$31,607/呎
 (25年-07月-14日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>B | 929呎 (3房)
+          <t>B | 1001呎 (3房)
 $3098万
-$33,348/呎
+$30,949/呎
 (24年-11月-11日)</t>
         </is>
       </c>
@@ -24956,17 +24956,17 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 977呎 (3房)
 $3080万
-$33,478/呎
+$31,525/呎
 (24年-04月-18日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>B | 929呎 (3房)
+          <t>B | 1001呎 (3房)
 $3078万
-$33,132/呎
+$30,749/呎
 (25年-07月-18日)</t>
         </is>
       </c>
@@ -24979,17 +24979,17 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 977呎 (3房)
 $3150万
-$34,239/呎
+$32,242/呎
 (24年-04月-17日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>B | 929呎 (3房)
+          <t>B | 1001呎 (3房)
 $3038万
-$32,702/呎
+$30,350/呎
 (25年-04月-24日)</t>
         </is>
       </c>
@@ -25002,17 +25002,17 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 977呎 (3房)
 $3028万
-$32,913/呎
+$30,993/呎
 (24年-04月-24日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>B | 929呎 (3房)
+          <t>B | 1001呎 (3房)
 $3080万
-$33,154/呎
+$30,769/呎
 (24年-08月-05日)</t>
         </is>
       </c>
@@ -25025,17 +25025,17 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 977呎 (3房)
 $3200万
-$34,783/呎
+$32,753/呎
 (24年-09月-19日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>B | 929呎 (3房)
+          <t>B | 1001呎 (3房)
 $3072万
-$33,068/呎
+$30,689/呎
 (24年-08月-05日)</t>
         </is>
       </c>
@@ -25048,17 +25048,17 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 977呎 (3房)
 $2988万
-$32,478/呎
+$30,583/呎
 (24年-03月-28日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>B | 929呎 (3房)
+          <t>B | 1001呎 (3房)
 $3018万
-$32,487/呎
+$30,150/呎
 (24年-10月-25日)</t>
         </is>
       </c>
@@ -25071,17 +25071,17 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 977呎 (3房)
 $2983万
-$32,424/呎
+$30,532/呎
 (24年-04月-16日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>B | 929呎 (3房)
+          <t>B | 1001呎 (3房)
 $2998万
-$32,271/呎
+$29,950/呎
 (24年-12月-30日)</t>
         </is>
       </c>
@@ -25102,9 +25102,9 @@
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>B | 929呎 (3房)
+          <t>B | 1001呎 (3房)
 $2988万
-$32,164/呎
+$29,850/呎
 (24年-11月-22日)</t>
         </is>
       </c>
@@ -25117,17 +25117,17 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 977呎 (3房)
 $2973万
-$32,315/呎
+$30,430/呎
 (24年-04月-18日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>B | 929呎 (3房)
+          <t>B | 1001呎 (3房)
 $3008万
-$32,379/呎
+$30,050/呎
 (24年-11月-27日)</t>
         </is>
       </c>
@@ -25140,17 +25140,17 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 977呎 (3房)
 $2968万
-$32,261/呎
+$30,379/呎
 (24年-04月-08日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>B | 929呎 (3房)
+          <t>B | 1001呎 (3房)
 $2919万
-$31,421/呎
+$29,161/呎
 (25年-04月-02日)</t>
         </is>
       </c>
@@ -25163,17 +25163,17 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 977呎 (3房)
 $2958万
-$32,152/呎
+$30,276/呎
 (24年-04月-16日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>B | 929呎 (3房)
+          <t>B | 1001呎 (3房)
 $3000万
-$32,293/呎
+$29,970/呎
 (24年-05月-28日)</t>
         </is>
       </c>
@@ -25186,17 +25186,17 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 977呎 (3房)
 $3000万
-$32,609/呎
+$30,706/呎
 (24年-08月-09日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>B | 929呎 (3房)
+          <t>B | 1001呎 (3房)
 $2880万
-$31,001/呎
+$28,771/呎
 (24年-11月-06日)</t>
         </is>
       </c>
@@ -25217,9 +25217,9 @@
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>B | 929呎 (3房)
+          <t>B | 1001呎 (3房)
 $2938万
-$31,625/呎
+$29,351/呎
 (24年-04月-29日)</t>
         </is>
       </c>
@@ -25240,9 +25240,9 @@
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>B | 929呎 (3房)
+          <t>B | 1001呎 (3房)
 $2860万
-$30,786/呎
+$28,571/呎
 (24年-11月-11日)</t>
         </is>
       </c>
@@ -25263,9 +25263,9 @@
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>B | 929呎 (3房)
+          <t>B | 1001呎 (3房)
 $2938万
-$31,625/呎
+$29,351/呎
 (25年-04月-17日)</t>
         </is>
       </c>
@@ -25278,17 +25278,17 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 977呎 (3房)
 $2850万
-$30,978/呎
+$29,171/呎
 (23年-12月-06日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>B | 929呎 (3房)
+          <t>B | 1001呎 (3房)
 $2828万
-$30,441/呎
+$28,252/呎
 (24年-07月-29日)</t>
         </is>
       </c>
@@ -25309,9 +25309,9 @@
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>B | 929呎 (3房)
+          <t>B | 1001呎 (3房)
 $2800万
-$30,140/呎
+$27,972/呎
 (24年-11月-05日)</t>
         </is>
       </c>
@@ -25332,9 +25332,9 @@
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>B | 929呎 (3房)
+          <t>B | 1001呎 (3房)
 $2788万
-$30,011/呎
+$27,852/呎
 (24年-11月-12日)</t>
         </is>
       </c>
@@ -25347,17 +25347,17 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 977呎 (3房)
 $2848万
-$30,957/呎
+$29,150/呎
 (24年-10月-31日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>B | 929呎 (3房)
+          <t>B | 1001呎 (3房)
 $2788万
-$30,011/呎
+$27,852/呎
 (24年-05月-20日)</t>
         </is>
       </c>
@@ -25378,9 +25378,9 @@
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>B | 929呎 (3房)
+          <t>B | 1001呎 (3房)
 $2770万
-$29,817/呎
+$27,672/呎
 (24年-11月-15日)</t>
         </is>
       </c>
@@ -25393,17 +25393,17 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 977呎 (3房)
 $2722万
-$29,587/呎
+$27,861/呎
 (24年-03月-27日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>B | 929呎 (3房)
+          <t>B | 1001呎 (3房)
 $2760万
-$29,709/呎
+$27,572/呎
 (24年-10月-08日)</t>
         </is>
       </c>
@@ -25416,17 +25416,17 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 977呎 (3房)
 $2700万
-$29,348/呎
+$27,636/呎
 (24年-03月-27日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>B | 929呎 (3房)
+          <t>B | 1001呎 (3房)
 $2750万
-$29,602/呎
+$27,473/呎
 (24年-05月-08日)</t>
         </is>
       </c>
@@ -25439,17 +25439,17 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 977呎 (3房)
 $2665万
-$28,967/呎
+$27,277/呎
 (24年-04月-08日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>B | 929呎 (3房)
+          <t>B | 1001呎 (3房)
 $2738万
-$29,473/呎
+$27,353/呎
 (24年-08月-19日)</t>
         </is>
       </c>
@@ -25462,17 +25462,17 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 977呎 (3房)
 $2633万
-$28,620/呎
+$26,950/呎
 (24年-04月-09日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
         <is>
-          <t>B | 929呎 (3房)
+          <t>B | 1001呎 (3房)
 $2702万
-$29,085/呎
+$26,993/呎
 (24年-11月-28日)</t>
         </is>
       </c>
@@ -25485,17 +25485,17 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 977呎 (3房)
 $2643万
-$28,728/呎
+$27,052/呎
 (24年-04月-11日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>B | 929呎 (3房)
+          <t>B | 1001呎 (3房)
 $2652万
-$28,547/呎
+$26,494/呎
 (25年-03月-24日)</t>
         </is>
       </c>
@@ -25508,17 +25508,17 @@
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>A | 869呎 (3房)
+          <t>A | 925呎 (3房)
 $2700万
-$31,070/呎
+$29,189/呎
 (25年-01月-27日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
         <is>
-          <t>B | 893呎 (3房)
+          <t>B | 964呎 (3房)
 $2945万
-$32,982/呎
+$30,553/呎
 (24年-12月-16日)</t>
         </is>
       </c>
@@ -25688,33 +25688,33 @@
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>C | 318呎 (1房)
+          <t>C | 317呎 (1房)
 $865万
-$27,210/呎
+$27,296/呎
 (25年-06月-24日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>D | 330呎 (1房)
+          <t>D | 331呎 (1房)
 $866万
-$26,254/呎
+$26,175/呎
 (25年-11月-14日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
         <is>
-          <t>E | 278呎 (开放式)
+          <t>E | 277呎 (开放式)
 $772万
-$27,782/呎
+$27,882/呎
 (25年-12月-15日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
         <is>
-          <t>F | 296呎 (开放式)
+          <t>F | 279呎 (开放式)
 $746万
-$25,195/呎
+$26,730/呎
 (25年-11月-26日)</t>
         </is>
       </c>
@@ -25744,17 +25744,17 @@
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>C | 318呎 (1房)
+          <t>C | 317呎 (1房)
 $848万
-$26,675/呎
+$26,759/呎
 (25年-06月-24日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>D | 330呎 (1房)
+          <t>D | 331呎 (1房)
 $849万
-$25,738/呎
+$25,661/呎
 (25年-08月-15日)</t>
         </is>
       </c>
@@ -25768,9 +25768,9 @@
       </c>
       <c r="G6" s="20" t="inlineStr">
         <is>
-          <t>F | 278呎 (开放式)
+          <t>F | 279呎 (开放式)
 $687万
-$24,699/呎
+$24,611/呎
 (25年-09月-17日)</t>
         </is>
       </c>
@@ -25800,25 +25800,25 @@
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>C | 318呎 (1房)
+          <t>C | 317呎 (1房)
 $959万
-$30,157/呎
+$30,252/呎
 (22年-02月-25日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
-          <t>D | 330呎 (1房)
+          <t>D | 331呎 (1房)
 $841万
-$25,483/呎
+$25,406/呎
 (25年-05月-29日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>E | 278呎 (开放式)
+          <t>E | 277呎 (开放式)
 $750万
-$26,969/呎
+$27,066/呎
 (25年-11月-12日)</t>
         </is>
       </c>
@@ -25832,9 +25832,9 @@
       </c>
       <c r="H7" s="20" t="inlineStr">
         <is>
-          <t>G | 330呎 (1房)
+          <t>G | 331呎 (1房)
 $854万
-$25,891/呎
+$25,813/呎
 (25年-06月-27日)</t>
         </is>
       </c>
@@ -25863,25 +25863,25 @@
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>C | 318呎 (1房)
+          <t>C | 317呎 (1房)
 $915万
-$28,765/呎
+$28,856/呎
 (23年-10月-06日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>D | 330呎 (1房)
+          <t>D | 331呎 (1房)
 $837万
-$25,357/呎
+$25,281/呎
 (25年-07月-25日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
-          <t>E | 278呎 (开放式)
+          <t>E | 277呎 (开放式)
 $778万
-$27,994/呎
+$28,095/呎
 (22年-01月-29日)</t>
         </is>
       </c>
@@ -25895,9 +25895,9 @@
       </c>
       <c r="H8" s="20" t="inlineStr">
         <is>
-          <t>G | 330呎 (1房)
+          <t>G | 331呎 (1房)
 $850万
-$25,763/呎
+$25,685/呎
 (25年-06月-27日)</t>
         </is>
       </c>
@@ -25926,17 +25926,17 @@
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>C | 318呎 (1房)
+          <t>C | 317呎 (1房)
 $910万
-$28,620/呎
+$28,710/呎
 (21年-10月-05日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>D | 330呎 (1房)
+          <t>D | 331呎 (1房)
 $837万
-$25,357/呎
+$25,281/呎
 (25年-06月-18日)</t>
         </is>
       </c>
@@ -25958,9 +25958,9 @@
       </c>
       <c r="H9" s="20" t="inlineStr">
         <is>
-          <t>G | 330呎 (1房)
+          <t>G | 331呎 (1房)
 $846万
-$25,638/呎
+$25,560/呎
 (25年-06月-23日)</t>
         </is>
       </c>
@@ -25989,17 +25989,17 @@
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>C | 318呎 (1房)
+          <t>C | 317呎 (1房)
 $945万
-$29,708/呎
+$29,802/呎
 (21年-09月-16日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>D | 330呎 (1房)
+          <t>D | 331呎 (1房)
 $828万
-$25,104/呎
+$25,028/呎
 (25年-06月-20日)</t>
         </is>
       </c>
@@ -26021,9 +26021,9 @@
       </c>
       <c r="H10" s="20" t="inlineStr">
         <is>
-          <t>G | 330呎 (1房)
+          <t>G | 331呎 (1房)
 $842万
-$25,508/呎
+$25,431/呎
 (25年-06月-25日)</t>
         </is>
       </c>
@@ -26060,9 +26060,9 @@
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>D | 330呎 (1房)
+          <t>D | 331呎 (1房)
 $824万
-$24,981/呎
+$24,905/呎
 (25年-06月-24日)</t>
         </is>
       </c>
@@ -26084,9 +26084,9 @@
       </c>
       <c r="H11" s="20" t="inlineStr">
         <is>
-          <t>G | 330呎 (1房)
+          <t>G | 331呎 (1房)
 $838万
-$25,382/呎
+$25,305/呎
 (25年-06月-24日)</t>
         </is>
       </c>
@@ -26115,25 +26115,25 @@
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>C | 318呎 (1房)
+          <t>C | 317呎 (1房)
 $935万
-$29,415/呎
+$29,508/呎
 (21年-07月-23日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>D | 330呎 (1房)
+          <t>D | 331呎 (1房)
 $820万
-$24,855/呎
+$24,780/呎
 (25年-06月-23日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>E | 278呎 (开放式)
+          <t>E | 277呎 (开放式)
 $763万
-$27,441/呎
+$27,540/呎
 (21年-11月-02日)</t>
         </is>
       </c>
@@ -26147,9 +26147,9 @@
       </c>
       <c r="H12" s="20" t="inlineStr">
         <is>
-          <t>G | 330呎 (1房)
+          <t>G | 331呎 (1房)
 $833万
-$25,256/呎
+$25,180/呎
 (25年-06月-27日)</t>
         </is>
       </c>
@@ -26178,17 +26178,17 @@
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>C | 318呎 (1房)
+          <t>C | 317呎 (1房)
 $815万
-$25,632/呎
+$25,713/呎
 (25年-06月-24日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
         <is>
-          <t>D | 330呎 (1房)
+          <t>D | 331呎 (1房)
 $816万
-$24,732/呎
+$24,657/呎
 (25年-06月-23日)</t>
         </is>
       </c>
@@ -26210,9 +26210,9 @@
       </c>
       <c r="H13" s="20" t="inlineStr">
         <is>
-          <t>G | 330呎 (1房)
+          <t>G | 331呎 (1房)
 $829万
-$25,128/呎
+$25,053/呎
 (25年-06月-23日)</t>
         </is>
       </c>
@@ -26241,25 +26241,25 @@
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>C | 318呎 (1房)
+          <t>C | 317呎 (1房)
 $926万
-$29,123/呎
+$29,215/呎
 (21年-09月-24日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>D | 330呎 (1房)
+          <t>D | 331呎 (1房)
 $812万
-$24,608/呎
+$24,534/呎
 (25年-06月-20日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
-          <t>E | 278呎 (开放式)
+          <t>E | 277呎 (开放式)
 $755万
-$27,171/呎
+$27,269/呎
 (21年-09月-18日)</t>
         </is>
       </c>
@@ -26273,9 +26273,9 @@
       </c>
       <c r="H14" s="20" t="inlineStr">
         <is>
-          <t>G | 330呎 (1房)
+          <t>G | 331呎 (1房)
 $903万
-$27,368/呎
+$27,285/呎
 (25年-05月-08日)</t>
         </is>
       </c>
@@ -26304,25 +26304,25 @@
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>C | 318呎 (1房)
+          <t>C | 317呎 (1房)
 $883万
-$27,777/呎
+$27,864/呎
 (21年-09月-24日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
         <is>
-          <t>D | 330呎 (1房)
+          <t>D | 331呎 (1房)
 $885万
-$26,804/呎
+$26,723/呎
 (24年-01月-12日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
-          <t>E | 278呎 (开放式)
+          <t>E | 277呎 (开放式)
 $752万
-$27,034/呎
+$27,131/呎
 (21年-10月-08日)</t>
         </is>
       </c>
@@ -26367,25 +26367,25 @@
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>C | 318呎 (1房)
+          <t>C | 317呎 (1房)
 $803万
-$25,251/呎
+$25,330/呎
 (25年-06月-25日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>D | 330呎 (1房)
+          <t>D | 331呎 (1房)
 $804万
-$24,364/呎
+$24,290/呎
 (25年-06月-26日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>E | 278呎 (开放式)
+          <t>E | 277呎 (开放式)
 $717万
-$25,786/呎
+$25,879/呎
 (26年-04月-16日)</t>
         </is>
       </c>
@@ -26399,9 +26399,9 @@
       </c>
       <c r="H16" s="20" t="inlineStr">
         <is>
-          <t>G | 330呎 (1房)
+          <t>G | 331呎 (1房)
 $817万
-$24,756/呎
+$24,682/呎
 (25年-06月-25日)</t>
         </is>
       </c>
@@ -26462,9 +26462,9 @@
       </c>
       <c r="H17" s="20" t="inlineStr">
         <is>
-          <t>G | 330呎 (1房)
+          <t>G | 331呎 (1房)
 $890万
-$26,963/呎
+$26,882/呎
 (24年-12月-19日)</t>
         </is>
       </c>
@@ -26501,17 +26501,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>D | 330呎 (1房)
+          <t>D | 331呎 (1房)
 $876万
-$26,536/呎
+$26,456/呎
 (21年-11月-18日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>E | 278呎 (开放式)
+          <t>E | 277呎 (开放式)
 $713万
-$25,658/呎
+$25,750/呎
 (26年-04月-29日)</t>
         </is>
       </c>
@@ -26525,9 +26525,9 @@
       </c>
       <c r="H18" s="20" t="inlineStr">
         <is>
-          <t>G | 330呎 (1房)
+          <t>G | 331呎 (1房)
 $813万
-$24,633/呎
+$24,559/呎
 (25年-06月-20日)</t>
         </is>
       </c>
@@ -26556,9 +26556,9 @@
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>C | 318呎 (1房)
+          <t>C | 317呎 (1房)
 $866万
-$27,229/呎
+$27,315/呎
 (21年-08月-02日)</t>
         </is>
       </c>
@@ -26572,9 +26572,9 @@
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>E | 278呎 (开放式)
+          <t>E | 277呎 (开放式)
 $737万
-$26,502/呎
+$26,597/呎
 (21年-08月-12日)</t>
         </is>
       </c>
@@ -26619,17 +26619,17 @@
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>C | 318呎 (1房)
+          <t>C | 317呎 (1房)
 $851万
-$26,762/呎
+$26,847/呎
 (21年-04月-28日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>D | 330呎 (1房)
+          <t>D | 331呎 (1房)
 $900万
-$27,273/呎
+$27,190/呎
 (21年-11月-11日)</t>
         </is>
       </c>
@@ -26651,9 +26651,9 @@
       </c>
       <c r="H20" s="20" t="inlineStr">
         <is>
-          <t>G | 330呎 (1房)
+          <t>G | 331呎 (1房)
 $877万
-$26,565/呎
+$26,485/呎
 (21年-11月-15日)</t>
         </is>
       </c>
@@ -26690,9 +26690,9 @@
       </c>
       <c r="E21" s="20" t="inlineStr">
         <is>
-          <t>D | 330呎 (1房)
+          <t>D | 331呎 (1房)
 $896万
-$27,137/呎
+$27,055/呎
 (21年-11月-12日)</t>
         </is>
       </c>
@@ -26840,9 +26840,9 @@
       </c>
       <c r="H23" s="20" t="inlineStr">
         <is>
-          <t>G | 330呎 (1房)
+          <t>G | 331呎 (1房)
 $789万
-$23,906/呎
+$23,834/呎
 (25年-06月-24日)</t>
         </is>
       </c>
@@ -26879,17 +26879,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>D | 330呎 (1房)
+          <t>D | 331呎 (1房)
 $846万
-$25,628/呎
+$25,550/呎
 (21年-11月-01日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>E | 278呎 (开放式)
+          <t>E | 277呎 (开放式)
 $689万
-$24,778/呎
+$24,867/呎
 (26年-04月-23日)</t>
         </is>
       </c>
@@ -26903,9 +26903,9 @@
       </c>
       <c r="H24" s="20" t="inlineStr">
         <is>
-          <t>G | 330呎 (1房)
+          <t>G | 331呎 (1房)
 $859万
-$26,040/呎
+$25,961/呎
 (21年-09月-24日)</t>
         </is>
       </c>
@@ -26934,25 +26934,25 @@
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>C | 318呎 (1房)
+          <t>C | 317呎 (1房)
 $866万
-$27,242/呎
+$27,328/呎
 (21年-04月-27日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
         <is>
-          <t>D | 330呎 (1房)
+          <t>D | 331呎 (1房)
 $769万
-$23,296/呎
+$23,226/呎
 (25年-06月-20日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>E | 278呎 (开放式)
+          <t>E | 277呎 (开放式)
 $685万
-$24,653/呎
+$24,742/呎
 (26年-04月-09日)</t>
         </is>
       </c>
@@ -26966,9 +26966,9 @@
       </c>
       <c r="H25" s="20" t="inlineStr">
         <is>
-          <t>G | 330呎 (1房)
+          <t>G | 331呎 (1房)
 $896万
-$27,165/呎
+$27,083/呎
 (21年-09月-23日)</t>
         </is>
       </c>
@@ -27005,17 +27005,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>D | 330呎 (1房)
+          <t>D | 331呎 (1房)
 $842万
-$25,500/呎
+$25,423/呎
 (21年-09月-25日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>E | 278呎 (开放式)
+          <t>E | 277呎 (开放式)
 $706万
-$25,413/呎
+$25,505/呎
 (21年-06月-29日)</t>
         </is>
       </c>
@@ -27068,9 +27068,9 @@
       </c>
       <c r="E27" s="20" t="inlineStr">
         <is>
-          <t>D | 330呎 (1房)
+          <t>D | 331呎 (1房)
 $761万
-$23,065/呎
+$22,996/呎
 (25年-06月-24日)</t>
         </is>
       </c>
@@ -27092,9 +27092,9 @@
       </c>
       <c r="H27" s="20" t="inlineStr">
         <is>
-          <t>G | 330呎 (1房)
+          <t>G | 331呎 (1房)
 $847万
-$25,652/呎
+$25,575/呎
 (21年-09月-23日)</t>
         </is>
       </c>
@@ -27123,9 +27123,9 @@
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>C | 318呎 (1房)
+          <t>C | 317呎 (1房)
 $853万
-$26,838/呎
+$26,923/呎
 (21年-04月-21日)</t>
         </is>
       </c>
@@ -27155,9 +27155,9 @@
       </c>
       <c r="H28" s="20" t="inlineStr">
         <is>
-          <t>G | 330呎 (1房)
+          <t>G | 331呎 (1房)
 $879万
-$26,628/呎
+$26,547/呎
 (21年-09月-15日)</t>
         </is>
       </c>
@@ -27194,17 +27194,17 @@
       </c>
       <c r="E29" s="20" t="inlineStr">
         <is>
-          <t>D | 330呎 (1房)
+          <t>D | 331呎 (1房)
 $863万
-$26,154/呎
+$26,075/呎
 (21年-11月-09日)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
         <is>
-          <t>E | 278呎 (开放式)
+          <t>E | 277呎 (开放式)
 $703万
-$25,286/呎
+$25,377/呎
 (21年-10月-21日)</t>
         </is>
       </c>
@@ -27249,9 +27249,9 @@
       </c>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>C | 318呎 (1房)
+          <t>C | 317呎 (1房)
 $860万
-$27,051/呎
+$27,136/呎
 (21年-08月-17日)</t>
         </is>
       </c>
@@ -27281,9 +27281,9 @@
       </c>
       <c r="H30" s="20" t="inlineStr">
         <is>
-          <t>G | 330呎 (1房)
+          <t>G | 331呎 (1房)
 $839万
-$25,424/呎
+$25,347/呎
 (22年-05月-05日)</t>
         </is>
       </c>
@@ -27320,9 +27320,9 @@
       </c>
       <c r="E31" s="20" t="inlineStr">
         <is>
-          <t>D | 330呎 (1房)
+          <t>D | 331呎 (1房)
 $850万
-$25,743/呎
+$25,665/呎
 (22年-06月-02日)</t>
         </is>
       </c>
@@ -27344,9 +27344,9 @@
       </c>
       <c r="H31" s="20" t="inlineStr">
         <is>
-          <t>G | 330呎 (1房)
+          <t>G | 331呎 (1房)
 $863万
-$26,153/呎
+$26,074/呎
 (22年-05月-31日)</t>
         </is>
       </c>
@@ -27359,17 +27359,17 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>A | 487呎 (2房)
+          <t>A | 486呎 (2房)
 $1500万
-$30,801/呎
+$30,864/呎
 (24年-04月-17日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>B | 294呎 (1房)
+          <t>B | 293呎 (1房)
 $810万
-$27,551/呎
+$27,645/呎
 (24年-10月-17日)</t>
         </is>
       </c>
@@ -27399,9 +27399,9 @@
       </c>
       <c r="G32" s="20" t="inlineStr">
         <is>
-          <t>F | 256呎 (开放式)
+          <t>F | 257呎 (开放式)
 $628万
-$24,531/呎
+$24,436/呎
 (24年-11月-04日)</t>
         </is>
       </c>
@@ -28828,17 +28828,17 @@
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>B | 291呎 (1房)
+          <t>B | 290呎 (1房)
 $808万
-$27,766/呎
+$27,862/呎
 (24年-04月-16日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>C | 411呎 (2房)
+          <t>C | 412呎 (2房)
 $1200万
-$29,197/呎
+$29,126/呎
 (24年-04月-05日)</t>
         </is>
       </c>
@@ -28852,9 +28852,9 @@
       </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
-          <t>E | 488呎 (2房)
+          <t>E | 487呎 (2房)
 $1468万
-$30,082/呎
+$30,144/呎
 (24年-07月-02日)</t>
         </is>
       </c>
